--- a/healthcare_surveys/037_vision_care_feedback_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/037_vision_care_feedback_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely likely'}</t>
+          <t>Extremely likely</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'likely'}</t>
+          <t>likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Likely'}</t>
+          <t>Likely</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Not likely'}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'not_likely_at_all'}</t>
+          <t>not_likely_at_all</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Not likely at all'}</t>
+          <t>Not likely at all</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'not_likely_at_all'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Not likely at all'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'excellent'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Excellent'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'good'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Good'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'average'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Average'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'fair'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Fair'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'poor'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Poor'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2,_'label':_false}</t>
+          <t>extremely_friendly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2, 'label': False}</t>
+          <t>Extremely friendly</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_friendly'}</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely friendly'}</t>
+          <t>Friendly</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'friendly'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Friendly'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_unfriendly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat unfriendly</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_unfriendly'}</t>
+          <t>not_friendly_at_all</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat unfriendly'}</t>
+          <t>Not friendly at all</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'not_friendly_at_all'}</t>
+          <t>extremely_friendly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Not friendly at all'}</t>
+          <t>Extremely friendly</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_friendly'}</t>
+          <t>friendly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely friendly'}</t>
+          <t>Friendly</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'friendly'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Friendly'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_unfriendly</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat unfriendly</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_unfriendly'}</t>
+          <t>not_friendly_at_all</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat unfriendly'}</t>
+          <t>Not friendly at all</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'not_friendly_at_all'}</t>
+          <t>extremely_clean</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Not friendly at all'}</t>
+          <t>Extremely clean</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'clean'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Clean'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_dirty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat dirty</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_dirty'}</t>
+          <t>extremely_dirty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat dirty'}</t>
+          <t>Extremely dirty</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'extremely_dirty'}</t>
+          <t>extremely_safe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Extremely dirty'}</t>
+          <t>Extremely safe</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_safe'}</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely safe'}</t>
+          <t>Safe</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'safe'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Safe'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_not_safe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat not safe</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_not_safe'}</t>
+          <t>not_safe_at_all</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat not safe'}</t>
+          <t>Not safe at all</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'not_safe_at_all'}</t>
+          <t>extremely_easy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Not safe at all'}</t>
+          <t>Extremely easy</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'easy'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Easy'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_difficult</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat difficult</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_difficult'}</t>
+          <t>extremely_difficult</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat difficult'}</t>
+          <t>Extremely difficult</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'extremely_difficult'}</t>
+          <t>extremely_clean</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Extremely difficult'}</t>
+          <t>Extremely clean</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_5,_'label':_'extremely_clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 5, 'label': 'Extremely clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_4,_'label':_'clean'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 4, 'label': 'Clean'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_'neutral'}</t>
+          <t>somewhat_dirty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 'Neutral'}</t>
+          <t>Somewhat dirty</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_2,_'label':_'somewhat_dirty'}</t>
+          <t>extremely_dirty</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 2, 'label': 'Somewhat dirty'}</t>
+          <t>Extremely dirty</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>question_22_choices</t>
+          <t>question_23_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_1,_'label':_'extremely_dirty'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 1, 'label': 'Extremely dirty'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'value':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
